--- a/Configs/GameConfig/Datas/模型配置.xlsx
+++ b/Configs/GameConfig/Datas/模型配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -102,13 +102,43 @@
     <t>模型路径</t>
   </si>
   <si>
-    <t>Towers/ArrowTower.prefab</t>
-  </si>
-  <si>
-    <t>Towers/Barracks.prefab</t>
-  </si>
-  <si>
-    <t>Towers/BannerTower.prefab</t>
+    <t>敌人</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala2D/Prefabs/AI/KoalaGuide.prefab</t>
+  </si>
+  <si>
+    <t>塔</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala2D/Prefabs/Weapons/Weapons/KoalaCannonWeapon.prefab</t>
+  </si>
+  <si>
+    <t>子弹</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala2D/Prefabs/Weapons/Projectiles/KoalaCannonBall.prefab</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala5D/Prefabs/AI/KoalaGuide.prefab</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala6D/Prefabs/AI/KoalaGuide.prefab</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala7D/Prefabs/AI/KoalaGuide.prefab</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala8D/Prefabs/AI/KoalaGuide.prefab</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala9D/Prefabs/AI/KoalaGuide.prefab</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala10D/Prefabs/AI/KoalaGuide.prefab</t>
+  </si>
+  <si>
+    <t>Assets/TopDownEngine/Demos/Koala11D/Prefabs/AI/KoalaGuide.prefab</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1226,7 @@
     <col min="1" max="1" width="9.29090909090909" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.5454545454545" style="2" customWidth="1"/>
     <col min="3" max="3" width="68.1818181818182" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.8181818181818" style="2" customWidth="1"/>
+    <col min="4" max="4" width="81.9090909090909" style="2" customWidth="1"/>
     <col min="5" max="5" width="32.5727272727273" style="2" customWidth="1"/>
     <col min="6" max="6" width="48.1454545454545" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1454545454545" style="1" customWidth="1"/>
@@ -1300,9 +1330,11 @@
       <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="15"/>
       <c r="K5" s="16"/>
@@ -1312,9 +1344,11 @@
       <c r="B6" s="15">
         <v>2</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" s="15"/>
       <c r="K6" s="16"/>
@@ -1324,9 +1358,11 @@
       <c r="B7" s="15">
         <v>3</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E7" s="15"/>
       <c r="K7" s="16"/>
@@ -1336,9 +1372,8 @@
       <c r="B8" s="15">
         <v>4</v>
       </c>
-      <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E8" s="15"/>
       <c r="K8" s="16"/>
@@ -1348,9 +1383,8 @@
       <c r="B9" s="15">
         <v>5</v>
       </c>
-      <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E9" s="15"/>
       <c r="K9" s="16"/>
@@ -1360,9 +1394,8 @@
       <c r="B10" s="15">
         <v>6</v>
       </c>
-      <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E10" s="15"/>
       <c r="K10" s="16"/>
@@ -1372,9 +1405,8 @@
       <c r="B11" s="15">
         <v>7</v>
       </c>
-      <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E11" s="15"/>
       <c r="K11" s="16"/>
@@ -1384,9 +1416,8 @@
       <c r="B12" s="15">
         <v>8</v>
       </c>
-      <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E12" s="15"/>
       <c r="K12" s="16"/>
@@ -1396,9 +1427,8 @@
       <c r="B13" s="15">
         <v>9</v>
       </c>
-      <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E13" s="15"/>
       <c r="K13" s="16"/>
@@ -1408,9 +1438,8 @@
       <c r="B14" s="15">
         <v>10</v>
       </c>
-      <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E14" s="15"/>
       <c r="K14" s="16"/>

--- a/Configs/GameConfig/Datas/模型配置.xlsx
+++ b/Configs/GameConfig/Datas/模型配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -58,6 +58,9 @@
     <t>path</t>
   </si>
   <si>
+    <t>offset</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>vector2</t>
   </si>
   <si>
     <t>##group</t>
@@ -102,12 +108,18 @@
     <t>模型路径</t>
   </si>
   <si>
+    <t>模型偏移</t>
+  </si>
+  <si>
     <t>敌人</t>
   </si>
   <si>
     <t>Assets/TopDownEngine/Demos/Koala2D/Prefabs/AI/KoalaGuide.prefab</t>
   </si>
   <si>
+    <t>0,0</t>
+  </si>
+  <si>
     <t>塔</t>
   </si>
   <si>
@@ -118,6 +130,9 @@
   </si>
   <si>
     <t>Assets/TopDownEngine/Demos/Koala2D/Prefabs/Weapons/Projectiles/KoalaCannonBall.prefab</t>
+  </si>
+  <si>
+    <t>2,0</t>
   </si>
   <si>
     <t>Assets/TopDownEngine/Demos/Koala5D/Prefabs/AI/KoalaGuide.prefab</t>
@@ -1226,7 +1241,7 @@
     <col min="1" max="1" width="9.29090909090909" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.5454545454545" style="2" customWidth="1"/>
     <col min="3" max="3" width="68.1818181818182" style="1" customWidth="1"/>
-    <col min="4" max="4" width="81.9090909090909" style="2" customWidth="1"/>
+    <col min="4" max="4" width="101.636363636364" style="2" customWidth="1"/>
     <col min="5" max="5" width="32.5727272727273" style="2" customWidth="1"/>
     <col min="6" max="6" width="48.1454545454545" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1454545454545" style="1" customWidth="1"/>
@@ -1251,7 +1266,9 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -1263,18 +1280,20 @@
     </row>
     <row r="2" ht="21.75" customHeight="1" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="10"/>
+        <v>7</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -1286,11 +1305,11 @@
     </row>
     <row r="3" ht="21.75" customHeight="1" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1305,18 +1324,20 @@
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5"/>
+        <v>14</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -1331,12 +1352,14 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="15"/>
+        <v>17</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="K5" s="16"/>
       <c r="L5" s="16"/>
     </row>
@@ -1345,12 +1368,14 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="15"/>
+        <v>20</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="K6" s="16"/>
       <c r="L6" s="16"/>
     </row>
@@ -1359,12 +1384,14 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>23</v>
+      </c>
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
     </row>
@@ -1373,9 +1400,11 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
     </row>
@@ -1384,9 +1413,11 @@
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="15"/>
+        <v>25</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
     </row>
@@ -1395,9 +1426,11 @@
         <v>6</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="15"/>
+        <v>26</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
     </row>
@@ -1406,9 +1439,11 @@
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="15"/>
+        <v>27</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
     </row>
@@ -1417,9 +1452,11 @@
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="15"/>
+        <v>28</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
     </row>
@@ -1428,9 +1465,11 @@
         <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
     </row>
@@ -1439,9 +1478,11 @@
         <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="15"/>
+        <v>30</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>18</v>
+      </c>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
     </row>

--- a/Configs/GameConfig/Datas/模型配置.xlsx
+++ b/Configs/GameConfig/Datas/模型配置.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,26 +27,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>i</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>d</t>
     </r>
@@ -84,19 +84,19 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>这是i</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>d</t>
     </r>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>Assets/TopDownEngine/Demos/Koala10D/Prefabs/AI/KoalaGuide.prefab</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>测试</t>
   </si>
   <si>
     <t>Assets/TopDownEngine/Demos/Koala11D/Prefabs/AI/KoalaGuide.prefab</t>
@@ -694,197 +700,197 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="6" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="7" applyFill="1" borderId="10" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="11" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="0" applyFill="0" borderId="12" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1231,29 +1237,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.29090909090909" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5454545454545" style="2" customWidth="1"/>
-    <col min="3" max="3" width="68.1818181818182" style="1" customWidth="1"/>
-    <col min="4" max="4" width="101.636363636364" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.5727272727273" style="2" customWidth="1"/>
-    <col min="6" max="6" width="48.1454545454545" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1454545454545" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.8636363636364" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.0090909090909" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.0090909090909" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.14545454545455" style="3" customWidth="1"/>
-    <col min="13" max="34" width="12.4363636363636" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.29090909090909" customWidth="1" style="1"/>
+    <col min="2" max="2" width="21.5454545454545" customWidth="1" style="2"/>
+    <col min="3" max="3" width="68.1818181818182" customWidth="1" style="1"/>
+    <col min="4" max="4" width="101.636363636364" customWidth="1" style="2"/>
+    <col min="5" max="5" width="32.5727272727273" customWidth="1" style="2"/>
+    <col min="6" max="6" width="48.1454545454545" customWidth="1" style="1"/>
+    <col min="7" max="7" width="13.1454545454545" customWidth="1" style="1"/>
+    <col min="8" max="8" width="12.4363636363636" customWidth="1" style="1"/>
+    <col min="9" max="9" width="17.8636363636364" customWidth="1" style="1"/>
+    <col min="10" max="10" width="28.0090909090909" customWidth="1" style="1"/>
+    <col min="11" max="11" width="13.0090909090909" customWidth="1" style="3"/>
+    <col min="12" max="12" width="5.14545454545455" customWidth="1" style="3"/>
+    <col min="13" max="34" width="12.4363636363636" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="1:13">
+    <row r="1" ht="21.75" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1278,7 +1284,7 @@
       <c r="L1" s="7"/>
       <c r="M1" s="8"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:13">
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>5</v>
       </c>
@@ -1303,7 +1309,7 @@
       <c r="L2" s="13"/>
       <c r="M2" s="8"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" spans="1:13">
+    <row r="3" ht="21.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -1322,7 +1328,7 @@
       <c r="L3" s="13"/>
       <c r="M3" s="8"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:13">
+    <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -1347,7 +1353,7 @@
       <c r="L4" s="4"/>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" ht="20.25" customHeight="1" spans="1:13">
+    <row r="5" ht="20.25" customHeight="1">
       <c r="B5" s="15">
         <v>1</v>
       </c>
@@ -1363,7 +1369,7 @@
       <c r="K5" s="16"/>
       <c r="L5" s="16"/>
     </row>
-    <row r="6" ht="20.25" customHeight="1" spans="1:13">
+    <row r="6" ht="20.25" customHeight="1">
       <c r="B6" s="15">
         <v>2</v>
       </c>
@@ -1379,7 +1385,7 @@
       <c r="K6" s="16"/>
       <c r="L6" s="16"/>
     </row>
-    <row r="7" ht="20.25" customHeight="1" spans="1:13">
+    <row r="7" ht="20.25" customHeight="1">
       <c r="B7" s="15">
         <v>3</v>
       </c>
@@ -1395,7 +1401,7 @@
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
     </row>
-    <row r="8" ht="20.25" customHeight="1" spans="1:13">
+    <row r="8" ht="20.25" customHeight="1">
       <c r="B8" s="15">
         <v>4</v>
       </c>
@@ -1408,7 +1414,7 @@
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
     </row>
-    <row r="9" ht="20.25" customHeight="1" spans="1:13">
+    <row r="9" ht="20.25" customHeight="1">
       <c r="B9" s="15">
         <v>5</v>
       </c>
@@ -1421,7 +1427,7 @@
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
     </row>
-    <row r="10" ht="20.25" customHeight="1" spans="1:13">
+    <row r="10" ht="20.25" customHeight="1">
       <c r="B10" s="15">
         <v>6</v>
       </c>
@@ -1434,7 +1440,7 @@
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
     </row>
-    <row r="11" ht="20.25" customHeight="1" spans="1:13">
+    <row r="11" ht="20.25" customHeight="1">
       <c r="B11" s="15">
         <v>7</v>
       </c>
@@ -1447,7 +1453,7 @@
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
     </row>
-    <row r="12" ht="20.25" customHeight="1" spans="1:13">
+    <row r="12" ht="20.25" customHeight="1">
       <c r="B12" s="15">
         <v>8</v>
       </c>
@@ -1460,7 +1466,7 @@
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
     </row>
-    <row r="13" ht="20.25" customHeight="1" spans="1:13">
+    <row r="13" ht="20.25" customHeight="1">
       <c r="B13" s="15">
         <v>9</v>
       </c>
@@ -1473,12 +1479,15 @@
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B14" s="15">
-        <v>10</v>
+    <row r="14" ht="20.25" customHeight="1">
+      <c r="B14" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>18</v>
@@ -1487,11 +1496,16 @@
       <c r="L14" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to AION.CoreGame under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Configs/GameConfig/Datas/模型配置.xlsx
+++ b/Configs/GameConfig/Datas/模型配置.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId1"/>
+    <sheet name="角色" sheetId="1" r:id="rId1"/>
+    <sheet name="子弹" sheetId="2" r:id="rId2"/>
+    <sheet name="塔" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,29 +29,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <color rgb="FF006100"/>
-        <sz val="11"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <color rgb="FF006100"/>
-        <sz val="11"/>
-      </rPr>
-      <t>d</t>
-    </r>
+    <t>id</t>
   </si>
   <si>
     <t>desc</t>
@@ -61,6 +46,9 @@
     <t>offset</t>
   </si>
   <si>
+    <t>scale</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -73,6 +61,9 @@
     <t>vector2</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -82,24 +73,7 @@
     <t>##</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <color rgb="FF006100"/>
-        <sz val="11"/>
-      </rPr>
-      <t>这是i</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <color rgb="FF006100"/>
-        <sz val="11"/>
-      </rPr>
-      <t>d</t>
-    </r>
+    <t>这是id</t>
   </si>
   <si>
     <t>描述</t>
@@ -111,55 +85,94 @@
     <t>模型偏移</t>
   </si>
   <si>
-    <t>敌人</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala2D/Prefabs/AI/KoalaGuide.prefab</t>
+    <t>模型scale</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Hero/Solider.prefab</t>
   </si>
   <si>
     <t>0,0</t>
   </si>
   <si>
-    <t>塔</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala2D/Prefabs/Weapons/Weapons/KoalaCannonWeapon.prefab</t>
-  </si>
-  <si>
-    <t>子弹</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala2D/Prefabs/Weapons/Projectiles/KoalaCannonBall.prefab</t>
-  </si>
-  <si>
-    <t>2,0</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala5D/Prefabs/AI/KoalaGuide.prefab</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala6D/Prefabs/AI/KoalaGuide.prefab</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala7D/Prefabs/AI/KoalaGuide.prefab</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala8D/Prefabs/AI/KoalaGuide.prefab</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala9D/Prefabs/AI/KoalaGuide.prefab</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala10D/Prefabs/AI/KoalaGuide.prefab</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>测试</t>
-  </si>
-  <si>
-    <t>Assets/TopDownEngine/Demos/Koala11D/Prefabs/AI/KoalaGuide.prefab</t>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Hero/Caster.prefab</t>
+  </si>
+  <si>
+    <t>弓箭手</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Hero/Archer.prefab</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Hero/Knight.prefab</t>
+  </si>
+  <si>
+    <t>不死族</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Monster/NormalMonster.prefab</t>
+  </si>
+  <si>
+    <t>不死族首领</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Monster/MidMonster.prefab</t>
+  </si>
+  <si>
+    <t>法师普攻</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Bullet/MagicalBullet.prefab</t>
+  </si>
+  <si>
+    <t>弓箭手箭矢</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Bullet/ArcherArrow.prefab</t>
+  </si>
+  <si>
+    <t>防御箭塔箭矢</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Bullet/DefenceTowerArrow.prefab</t>
+  </si>
+  <si>
+    <t>法师营地</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Tower/MagicCamp.prefab</t>
+  </si>
+  <si>
+    <t>战士营地</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Tower/WarriorCamp.prefab</t>
+  </si>
+  <si>
+    <t>骑士营地</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Tower/KnitCamp.prefab</t>
+  </si>
+  <si>
+    <t>射手营地</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Tower/ArcherCamp.prefab</t>
+  </si>
+  <si>
+    <t>弓箭塔</t>
+  </si>
+  <si>
+    <t>Assets/Game/Prefab/LocalResources/Tower/TowerArrow.prefab</t>
   </si>
 </sst>
 </file>
@@ -188,14 +201,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -700,197 +713,197 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="6" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="7" applyFill="1" borderId="10" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="11" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="0" applyFill="0" borderId="12" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1237,266 +1250,273 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.29090909090909" customWidth="1" style="1"/>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1" style="2"/>
-    <col min="3" max="3" width="68.1818181818182" customWidth="1" style="1"/>
-    <col min="4" max="4" width="101.636363636364" customWidth="1" style="2"/>
-    <col min="5" max="5" width="32.5727272727273" customWidth="1" style="2"/>
-    <col min="6" max="6" width="48.1454545454545" customWidth="1" style="1"/>
-    <col min="7" max="7" width="13.1454545454545" customWidth="1" style="1"/>
-    <col min="8" max="8" width="12.4363636363636" customWidth="1" style="1"/>
-    <col min="9" max="9" width="17.8636363636364" customWidth="1" style="1"/>
-    <col min="10" max="10" width="28.0090909090909" customWidth="1" style="1"/>
-    <col min="11" max="11" width="13.0090909090909" customWidth="1" style="3"/>
-    <col min="12" max="12" width="5.14545454545455" customWidth="1" style="3"/>
-    <col min="13" max="34" width="12.4363636363636" customWidth="1" style="1"/>
+    <col min="1" max="1" width="9.29090909090909" style="5" customWidth="1"/>
+    <col min="2" max="2" width="21.5454545454545" style="7" customWidth="1"/>
+    <col min="3" max="3" width="68.1818181818182" style="5" customWidth="1"/>
+    <col min="4" max="4" width="101.636363636364" style="7" customWidth="1"/>
+    <col min="5" max="5" width="32.5727272727273" style="7" customWidth="1"/>
+    <col min="6" max="6" width="48.1454545454545" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.1454545454545" style="5" customWidth="1"/>
+    <col min="8" max="8" width="12.4363636363636" style="5" customWidth="1"/>
+    <col min="9" max="9" width="17.8636363636364" style="5" customWidth="1"/>
+    <col min="10" max="10" width="28.0090909090909" style="5" customWidth="1"/>
+    <col min="11" max="11" width="13.0090909090909" style="8" customWidth="1"/>
+    <col min="12" max="12" width="5.14545454545455" style="8" customWidth="1"/>
+    <col min="13" max="34" width="12.4363636363636" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="8"/>
-    </row>
-    <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="11"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="8"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="9" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="8"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="11"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="11"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="8"/>
-    </row>
-    <row r="5" ht="20.25" customHeight="1">
-      <c r="B5" s="15">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F4" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="11"/>
+    </row>
+    <row r="5" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B5" s="6">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.65</v>
       </c>
       <c r="K5" s="16"/>
       <c r="L5" s="16"/>
     </row>
-    <row r="6" ht="20.25" customHeight="1">
-      <c r="B6" s="15">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>18</v>
+    <row r="6" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B6" s="6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.65</v>
       </c>
       <c r="K6" s="16"/>
       <c r="L6" s="16"/>
     </row>
-    <row r="7" ht="20.25" customHeight="1">
-      <c r="B7" s="15">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
+    <row r="7" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B7" s="6">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>23</v>
+      <c r="F7" s="5">
+        <v>0.65</v>
       </c>
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
     </row>
-    <row r="8" ht="20.25" customHeight="1">
-      <c r="B8" s="15">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>18</v>
+    <row r="8" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B8" s="6">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.65</v>
       </c>
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
     </row>
-    <row r="9" ht="20.25" customHeight="1">
-      <c r="B9" s="15">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>18</v>
+    <row r="9" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B9" s="6">
+        <v>2001</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.65</v>
       </c>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
     </row>
-    <row r="10" ht="20.25" customHeight="1">
-      <c r="B10" s="15">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>18</v>
+    <row r="10" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B10" s="6">
+        <v>2002</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.65</v>
       </c>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
     </row>
-    <row r="11" ht="20.25" customHeight="1">
-      <c r="B11" s="15">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>18</v>
-      </c>
+    <row r="11" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B11" s="6"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6"/>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
     </row>
-    <row r="12" ht="20.25" customHeight="1">
-      <c r="B12" s="15">
-        <v>8</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>18</v>
-      </c>
+    <row r="12" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B12" s="6"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
     </row>
-    <row r="13" ht="20.25" customHeight="1">
-      <c r="B13" s="15">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>18</v>
-      </c>
+    <row r="13" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B13" s="6"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" ht="20.25" customHeight="1">
-      <c r="B14" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>18</v>
-      </c>
+    <row r="14" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B14" s="6"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
@@ -1505,7 +1525,346 @@
 </worksheet>
 </file>
 
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to AION.CoreGame under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="53.4545454545455" customWidth="1"/>
+    <col min="3" max="3" width="62.6363636363636" customWidth="1"/>
+    <col min="4" max="4" width="74.3636363636364" customWidth="1"/>
+    <col min="5" max="5" width="54.5454545454545" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="14.5" spans="1:6">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6">
+        <v>11002</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5" spans="1:6">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6">
+        <v>11003</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5" spans="1:6">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6">
+        <v>13005</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" spans="1:6">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" ht="14.5" spans="1:6">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" ht="14.5" spans="1:6">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="62.6363636363636" customWidth="1"/>
+    <col min="3" max="3" width="56.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="61.0909090909091" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="14.5" spans="1:6">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6">
+        <v>3001</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5" spans="1:6">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6">
+        <v>3002</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5" spans="1:6">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6">
+        <v>3003</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>3004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>3005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9">
+        <v>0.92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>